--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1135"/>
+  <dimension ref="A1:I1141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37550,7 +37550,7 @@
         </is>
       </c>
       <c r="G1125" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1125" t="n">
         <v>568.1</v>
@@ -37583,7 +37583,7 @@
         </is>
       </c>
       <c r="G1126" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1126" t="n">
         <v>5783</v>
@@ -37616,7 +37616,7 @@
         </is>
       </c>
       <c r="G1127" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1127" t="n">
         <v>2889</v>
@@ -37649,7 +37649,7 @@
         </is>
       </c>
       <c r="G1128" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1128" t="n">
         <v>21.41</v>
@@ -37682,7 +37682,7 @@
         </is>
       </c>
       <c r="G1129" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1129" t="n">
         <v>72.54000000000001</v>
@@ -37715,7 +37715,7 @@
         </is>
       </c>
       <c r="G1130" s="1" t="n">
-        <v>46238.63042275196</v>
+        <v>46238.63042275463</v>
       </c>
       <c r="H1130" t="n">
         <v>8.991</v>
@@ -37747,9 +37747,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1131" t="inlineStr"/>
-      <c r="H1131" t="inlineStr"/>
-      <c r="I1131" t="inlineStr"/>
+      <c r="G1131" s="1" t="n">
+        <v>46239.54741965623</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>22.575</v>
+      </c>
+      <c r="I1131" t="n">
+        <v>-4.999999999999996</v>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" s="1" t="n">
@@ -37855,9 +37861,177 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1135" t="inlineStr"/>
-      <c r="H1135" t="inlineStr"/>
-      <c r="I1135" t="inlineStr"/>
+      <c r="G1135" s="1" t="n">
+        <v>46239.54741965623</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>1921.5</v>
+      </c>
+      <c r="I1135" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>21.2515</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>24.1596</v>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr"/>
+      <c r="H1136" t="inlineStr"/>
+      <c r="I1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>5838</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>6129.900000000001</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>5546.099999999999</v>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr"/>
+      <c r="H1137" t="inlineStr"/>
+      <c r="I1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>4568.5</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>4796.925</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>4340.075</v>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr"/>
+      <c r="H1138" t="inlineStr"/>
+      <c r="I1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>HYDR</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr"/>
+      <c r="H1139" t="inlineStr"/>
+      <c r="I1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>2929</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>3075.45</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>2782.55</v>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr"/>
+      <c r="H1140" t="inlineStr"/>
+      <c r="I1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>27.6255</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>24.9945</v>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr"/>
+      <c r="H1141" t="inlineStr"/>
+      <c r="I1141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1141"/>
+  <dimension ref="A1:I1146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37748,7 +37748,7 @@
         </is>
       </c>
       <c r="G1131" s="1" t="n">
-        <v>46239.54741965623</v>
+        <v>46239.54741965278</v>
       </c>
       <c r="H1131" t="n">
         <v>22.575</v>
@@ -37780,9 +37780,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1132" t="inlineStr"/>
-      <c r="H1132" t="inlineStr"/>
-      <c r="I1132" t="inlineStr"/>
+      <c r="G1132" s="1" t="n">
+        <v>46240.54868269176</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>61.992</v>
+      </c>
+      <c r="I1132" t="n">
+        <v>-4.999999999999996</v>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" s="1" t="n">
@@ -37834,9 +37840,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1134" t="inlineStr"/>
-      <c r="H1134" t="inlineStr"/>
-      <c r="I1134" t="inlineStr"/>
+      <c r="G1134" s="1" t="n">
+        <v>46240.54868269176</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>26.964</v>
+      </c>
+      <c r="I1134" t="n">
+        <v>-4.999999999999996</v>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" s="1" t="n">
@@ -37862,7 +37874,7 @@
         </is>
       </c>
       <c r="G1135" s="1" t="n">
-        <v>46239.54741965623</v>
+        <v>46239.54741965278</v>
       </c>
       <c r="H1135" t="n">
         <v>1921.5</v>
@@ -37975,9 +37987,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1139" t="inlineStr"/>
-      <c r="H1139" t="inlineStr"/>
-      <c r="I1139" t="inlineStr"/>
+      <c r="G1139" s="1" t="n">
+        <v>46240.54868269176</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="I1139" t="n">
+        <v>-4.999999999999988</v>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" s="1" t="n">
@@ -38029,9 +38047,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1141" t="inlineStr"/>
-      <c r="H1141" t="inlineStr"/>
-      <c r="I1141" t="inlineStr"/>
+      <c r="G1141" s="1" t="n">
+        <v>46240.54868269176</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>27.6255</v>
+      </c>
+      <c r="I1141" t="n">
+        <v>-5.000000000000001</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr"/>
+      <c r="H1142" t="inlineStr"/>
+      <c r="I1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>17.115</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>15.485</v>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr"/>
+      <c r="H1143" t="inlineStr"/>
+      <c r="I1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>24.4335</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>22.1065</v>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr"/>
+      <c r="H1144" t="inlineStr"/>
+      <c r="I1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>4612.5</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>4843.125</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>4381.875</v>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr"/>
+      <c r="H1145" t="inlineStr"/>
+      <c r="I1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>75.06</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>78.813</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>71.307</v>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr"/>
+      <c r="H1146" t="inlineStr"/>
+      <c r="I1146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1146"/>
+  <dimension ref="A1:I1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37781,7 +37781,7 @@
         </is>
       </c>
       <c r="G1132" s="1" t="n">
-        <v>46240.54868269176</v>
+        <v>46240.54868269676</v>
       </c>
       <c r="H1132" t="n">
         <v>61.992</v>
@@ -37813,9 +37813,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1133" t="inlineStr"/>
-      <c r="H1133" t="inlineStr"/>
-      <c r="I1133" t="inlineStr"/>
+      <c r="G1133" s="1" t="n">
+        <v>46241.48253590146</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="I1133" t="n">
+        <v>-8.506841165972642</v>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" s="1" t="n">
@@ -37841,7 +37847,7 @@
         </is>
       </c>
       <c r="G1134" s="1" t="n">
-        <v>46240.54868269176</v>
+        <v>46240.54868269676</v>
       </c>
       <c r="H1134" t="n">
         <v>26.964</v>
@@ -37988,7 +37994,7 @@
         </is>
       </c>
       <c r="G1139" s="1" t="n">
-        <v>46240.54868269176</v>
+        <v>46240.54868269676</v>
       </c>
       <c r="H1139" t="n">
         <v>0.357</v>
@@ -38048,7 +38054,7 @@
         </is>
       </c>
       <c r="G1141" s="1" t="n">
-        <v>46240.54868269176</v>
+        <v>46240.54868269676</v>
       </c>
       <c r="H1141" t="n">
         <v>27.6255</v>
@@ -38107,9 +38113,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1143" t="inlineStr"/>
-      <c r="H1143" t="inlineStr"/>
-      <c r="I1143" t="inlineStr"/>
+      <c r="G1143" s="1" t="n">
+        <v>46241.48253590146</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>17.115</v>
+      </c>
+      <c r="I1143" t="n">
+        <v>-4.999999999999986</v>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" s="1" t="n">
@@ -38191,6 +38203,141 @@
       <c r="G1146" t="inlineStr"/>
       <c r="H1146" t="inlineStr"/>
       <c r="I1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>5828</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>6119.400000000001</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>5536.599999999999</v>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr"/>
+      <c r="H1147" t="inlineStr"/>
+      <c r="I1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>4660</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>4893</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>4427</v>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr"/>
+      <c r="H1148" t="inlineStr"/>
+      <c r="I1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>63.378</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>57.342</v>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr"/>
+      <c r="H1149" t="inlineStr"/>
+      <c r="I1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>2910</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>3055.5</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>2764.5</v>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr"/>
+      <c r="H1150" t="inlineStr"/>
+      <c r="I1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>23.205</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>20.995</v>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr"/>
+      <c r="H1151" t="inlineStr"/>
+      <c r="I1151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1151"/>
+  <dimension ref="A1:I1156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37814,7 +37814,7 @@
         </is>
       </c>
       <c r="G1133" s="1" t="n">
-        <v>46241.48253590146</v>
+        <v>46241.48253590277</v>
       </c>
       <c r="H1133" t="n">
         <v>91.2</v>
@@ -37912,9 +37912,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1136" t="inlineStr"/>
-      <c r="H1136" t="inlineStr"/>
-      <c r="I1136" t="inlineStr"/>
+      <c r="G1136" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="I1136" t="n">
+        <v>-0.2682163611980433</v>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" s="1" t="n">
@@ -37939,9 +37945,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1137" t="inlineStr"/>
-      <c r="H1137" t="inlineStr"/>
-      <c r="I1137" t="inlineStr"/>
+      <c r="G1137" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>5644</v>
+      </c>
+      <c r="I1137" t="n">
+        <v>3.323055841041452</v>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" s="1" t="n">
@@ -37966,9 +37978,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1138" t="inlineStr"/>
-      <c r="H1138" t="inlineStr"/>
-      <c r="I1138" t="inlineStr"/>
+      <c r="G1138" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>4667.5</v>
+      </c>
+      <c r="I1138" t="n">
+        <v>-2.167013242858706</v>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="1" t="n">
@@ -38026,9 +38044,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1140" t="inlineStr"/>
-      <c r="H1140" t="inlineStr"/>
-      <c r="I1140" t="inlineStr"/>
+      <c r="G1140" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>2949</v>
+      </c>
+      <c r="I1140" t="n">
+        <v>-0.6828269033799932</v>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" s="1" t="n">
@@ -38086,9 +38110,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1142" t="inlineStr"/>
-      <c r="H1142" t="inlineStr"/>
-      <c r="I1142" t="inlineStr"/>
+      <c r="G1142" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="I1142" t="n">
+        <v>4.984025559105438</v>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="1" t="n">
@@ -38114,7 +38144,7 @@
         </is>
       </c>
       <c r="G1143" s="1" t="n">
-        <v>46241.48253590146</v>
+        <v>46241.48253590277</v>
       </c>
       <c r="H1143" t="n">
         <v>17.115</v>
@@ -38146,9 +38176,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1144" t="inlineStr"/>
-      <c r="H1144" t="inlineStr"/>
-      <c r="I1144" t="inlineStr"/>
+      <c r="G1144" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="I1144" t="n">
+        <v>4.125483455092398</v>
+      </c>
     </row>
     <row r="1145">
       <c r="A1145" s="1" t="n">
@@ -38173,9 +38209,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1145" t="inlineStr"/>
-      <c r="H1145" t="inlineStr"/>
-      <c r="I1145" t="inlineStr"/>
+      <c r="G1145" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>4667.5</v>
+      </c>
+      <c r="I1145" t="n">
+        <v>-1.192411924119241</v>
+      </c>
     </row>
     <row r="1146">
       <c r="A1146" s="1" t="n">
@@ -38200,9 +38242,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1146" t="inlineStr"/>
-      <c r="H1146" t="inlineStr"/>
-      <c r="I1146" t="inlineStr"/>
+      <c r="G1146" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="I1146" t="n">
+        <v>1.891819877431391</v>
+      </c>
     </row>
     <row r="1147">
       <c r="A1147" s="1" t="n">
@@ -38227,9 +38275,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1147" t="inlineStr"/>
-      <c r="H1147" t="inlineStr"/>
-      <c r="I1147" t="inlineStr"/>
+      <c r="G1147" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>5644</v>
+      </c>
+      <c r="I1147" t="n">
+        <v>3.157172271791352</v>
+      </c>
     </row>
     <row r="1148">
       <c r="A1148" s="1" t="n">
@@ -38254,9 +38308,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1148" t="inlineStr"/>
-      <c r="H1148" t="inlineStr"/>
-      <c r="I1148" t="inlineStr"/>
+      <c r="G1148" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>4667.5</v>
+      </c>
+      <c r="I1148" t="n">
+        <v>-0.1609442060085837</v>
+      </c>
     </row>
     <row r="1149">
       <c r="A1149" s="1" t="n">
@@ -38281,9 +38341,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1149" t="inlineStr"/>
-      <c r="H1149" t="inlineStr"/>
-      <c r="I1149" t="inlineStr"/>
+      <c r="G1149" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="I1149" t="n">
+        <v>1.457919151756134</v>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" s="1" t="n">
@@ -38308,9 +38374,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1150" t="inlineStr"/>
-      <c r="H1150" t="inlineStr"/>
-      <c r="I1150" t="inlineStr"/>
+      <c r="G1150" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>2949</v>
+      </c>
+      <c r="I1150" t="n">
+        <v>-1.34020618556701</v>
+      </c>
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
@@ -38335,9 +38407,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1151" t="inlineStr"/>
-      <c r="H1151" t="inlineStr"/>
-      <c r="I1151" t="inlineStr"/>
+      <c r="G1151" s="1" t="n">
+        <v>46244.49834138972</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="I1151" t="n">
+        <v>1.312217194570148</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>5578</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>5856.900000000001</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>5299.099999999999</v>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr"/>
+      <c r="H1152" t="inlineStr"/>
+      <c r="I1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>4628.5</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>4859.925</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>4397.075</v>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr"/>
+      <c r="H1153" t="inlineStr"/>
+      <c r="I1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>60.58500000000001</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>54.815</v>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr"/>
+      <c r="H1154" t="inlineStr"/>
+      <c r="I1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>22.8795</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>20.7005</v>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr"/>
+      <c r="H1155" t="inlineStr"/>
+      <c r="I1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>89.40750000000001</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>80.8925</v>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr"/>
+      <c r="H1156" t="inlineStr"/>
+      <c r="I1156" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -37913,7 +37913,7 @@
         </is>
       </c>
       <c r="G1136" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1136" t="n">
         <v>22.31</v>
@@ -37946,7 +37946,7 @@
         </is>
       </c>
       <c r="G1137" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1137" t="n">
         <v>5644</v>
@@ -37979,7 +37979,7 @@
         </is>
       </c>
       <c r="G1138" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1138" t="n">
         <v>4667.5</v>
@@ -38045,7 +38045,7 @@
         </is>
       </c>
       <c r="G1140" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1140" t="n">
         <v>2949</v>
@@ -38111,7 +38111,7 @@
         </is>
       </c>
       <c r="G1142" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1142" t="n">
         <v>59.48</v>
@@ -38177,7 +38177,7 @@
         </is>
       </c>
       <c r="G1144" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1144" t="n">
         <v>22.31</v>
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="G1145" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1145" t="n">
         <v>4667.5</v>
@@ -38243,7 +38243,7 @@
         </is>
       </c>
       <c r="G1146" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1146" t="n">
         <v>73.64</v>
@@ -38276,7 +38276,7 @@
         </is>
       </c>
       <c r="G1147" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1147" t="n">
         <v>5644</v>
@@ -38309,7 +38309,7 @@
         </is>
       </c>
       <c r="G1148" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1148" t="n">
         <v>4667.5</v>
@@ -38342,7 +38342,7 @@
         </is>
       </c>
       <c r="G1149" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1149" t="n">
         <v>59.48</v>
@@ -38375,7 +38375,7 @@
         </is>
       </c>
       <c r="G1150" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1150" t="n">
         <v>2949</v>
@@ -38408,7 +38408,7 @@
         </is>
       </c>
       <c r="G1151" s="1" t="n">
-        <v>46244.49834138972</v>
+        <v>46244.49834138889</v>
       </c>
       <c r="H1151" t="n">
         <v>21.81</v>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1156"/>
+  <dimension ref="A1:I1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38494,9 +38494,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1154" t="inlineStr"/>
-      <c r="H1154" t="inlineStr"/>
-      <c r="I1154" t="inlineStr"/>
+      <c r="G1154" s="1" t="n">
+        <v>46246.49069762709</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>60.58500000000001</v>
+      </c>
+      <c r="I1154" t="n">
+        <v>-5.000000000000009</v>
+      </c>
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
@@ -38548,9 +38554,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1156" t="inlineStr"/>
-      <c r="H1156" t="inlineStr"/>
-      <c r="I1156" t="inlineStr"/>
+      <c r="G1156" s="1" t="n">
+        <v>46246.49069762709</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>89.40750000000001</v>
+      </c>
+      <c r="I1156" t="n">
+        <v>-5.000000000000009</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>67.72500000000001</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>61.275</v>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr"/>
+      <c r="H1157" t="inlineStr"/>
+      <c r="I1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>3212.5</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>3373.125</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>3051.875</v>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr"/>
+      <c r="H1158" t="inlineStr"/>
+      <c r="I1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>80.304</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>72.65600000000001</v>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr"/>
+      <c r="H1159" t="inlineStr"/>
+      <c r="I1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>22.595</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>23.72475</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>21.46525</v>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr"/>
+      <c r="H1160" t="inlineStr"/>
+      <c r="I1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>29.5365</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>26.7235</v>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="inlineStr"/>
+      <c r="I1161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1161"/>
+  <dimension ref="A1:I1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38440,9 +38440,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1152" t="inlineStr"/>
-      <c r="H1152" t="inlineStr"/>
-      <c r="I1152" t="inlineStr"/>
+      <c r="G1152" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>5538</v>
+      </c>
+      <c r="I1152" t="n">
+        <v>0.7171029042667623</v>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
@@ -38467,9 +38473,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1153" t="inlineStr"/>
-      <c r="H1153" t="inlineStr"/>
-      <c r="I1153" t="inlineStr"/>
+      <c r="G1153" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>4585</v>
+      </c>
+      <c r="I1153" t="n">
+        <v>0.9398293183536783</v>
+      </c>
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
@@ -38495,7 +38507,7 @@
         </is>
       </c>
       <c r="G1154" s="1" t="n">
-        <v>46246.49069762709</v>
+        <v>46246.49069762731</v>
       </c>
       <c r="H1154" t="n">
         <v>60.58500000000001</v>
@@ -38527,9 +38539,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1155" t="inlineStr"/>
-      <c r="H1155" t="inlineStr"/>
-      <c r="I1155" t="inlineStr"/>
+      <c r="G1155" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="I1155" t="n">
+        <v>6.287287746672774</v>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
@@ -38555,7 +38573,7 @@
         </is>
       </c>
       <c r="G1156" s="1" t="n">
-        <v>46246.49069762709</v>
+        <v>46246.49069762731</v>
       </c>
       <c r="H1156" t="n">
         <v>89.40750000000001</v>
@@ -38587,9 +38605,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1157" t="inlineStr"/>
-      <c r="H1157" t="inlineStr"/>
-      <c r="I1157" t="inlineStr"/>
+      <c r="G1157" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>61.275</v>
+      </c>
+      <c r="I1157" t="n">
+        <v>5.000000000000003</v>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
@@ -38641,9 +38665,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1159" t="inlineStr"/>
-      <c r="H1159" t="inlineStr"/>
-      <c r="I1159" t="inlineStr"/>
+      <c r="G1159" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>72.65600000000001</v>
+      </c>
+      <c r="I1159" t="n">
+        <v>4.999999999999997</v>
+      </c>
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
@@ -38668,9 +38698,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1160" t="inlineStr"/>
-      <c r="H1160" t="inlineStr"/>
-      <c r="I1160" t="inlineStr"/>
+      <c r="G1160" s="1" t="n">
+        <v>46247.49351137623</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>21.46525</v>
+      </c>
+      <c r="I1160" t="n">
+        <v>4.99999999999999</v>
+      </c>
     </row>
     <row r="1161">
       <c r="A1161" s="1" t="n">
@@ -38698,6 +38734,141 @@
       <c r="G1161" t="inlineStr"/>
       <c r="H1161" t="inlineStr"/>
       <c r="I1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>BANEP</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>920.5</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>966.5250000000001</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>874.4749999999999</v>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr"/>
+      <c r="H1162" t="inlineStr"/>
+      <c r="I1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>5578</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>5856.900000000001</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>5299.099999999999</v>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr"/>
+      <c r="H1163" t="inlineStr"/>
+      <c r="I1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>4662</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>4895.1</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>4428.9</v>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr"/>
+      <c r="H1164" t="inlineStr"/>
+      <c r="I1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>22.407</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>20.273</v>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr"/>
+      <c r="H1165" t="inlineStr"/>
+      <c r="I1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>64.995</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>58.80499999999999</v>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr"/>
+      <c r="H1166" t="inlineStr"/>
+      <c r="I1166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1166"/>
+  <dimension ref="A1:I1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38441,7 +38441,7 @@
         </is>
       </c>
       <c r="G1152" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1152" t="n">
         <v>5538</v>
@@ -38474,7 +38474,7 @@
         </is>
       </c>
       <c r="G1153" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1153" t="n">
         <v>4585</v>
@@ -38540,7 +38540,7 @@
         </is>
       </c>
       <c r="G1155" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1155" t="n">
         <v>20.42</v>
@@ -38606,7 +38606,7 @@
         </is>
       </c>
       <c r="G1157" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1157" t="n">
         <v>61.275</v>
@@ -38666,7 +38666,7 @@
         </is>
       </c>
       <c r="G1159" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1159" t="n">
         <v>72.65600000000001</v>
@@ -38699,7 +38699,7 @@
         </is>
       </c>
       <c r="G1160" s="1" t="n">
-        <v>46247.49351137623</v>
+        <v>46247.49351137732</v>
       </c>
       <c r="H1160" t="n">
         <v>21.46525</v>
@@ -38731,9 +38731,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1161" t="inlineStr"/>
-      <c r="H1161" t="inlineStr"/>
-      <c r="I1161" t="inlineStr"/>
+      <c r="G1161" s="1" t="n">
+        <v>46248.4888023993</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>26.7235</v>
+      </c>
+      <c r="I1161" t="n">
+        <v>4.999999999999992</v>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" s="1" t="n">
@@ -38758,9 +38764,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1162" t="inlineStr"/>
-      <c r="H1162" t="inlineStr"/>
-      <c r="I1162" t="inlineStr"/>
+      <c r="G1162" s="1" t="n">
+        <v>46248.4888023993</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>874.4749999999999</v>
+      </c>
+      <c r="I1162" t="n">
+        <v>5.00000000000001</v>
+      </c>
     </row>
     <row r="1163">
       <c r="A1163" s="1" t="n">
@@ -38839,9 +38851,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1165" t="inlineStr"/>
-      <c r="H1165" t="inlineStr"/>
-      <c r="I1165" t="inlineStr"/>
+      <c r="G1165" s="1" t="n">
+        <v>46248.4888023993</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>20.273</v>
+      </c>
+      <c r="I1165" t="n">
+        <v>5.000000000000001</v>
+      </c>
     </row>
     <row r="1166">
       <c r="A1166" s="1" t="n">
@@ -38866,9 +38884,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1166" t="inlineStr"/>
-      <c r="H1166" t="inlineStr"/>
-      <c r="I1166" t="inlineStr"/>
+      <c r="G1166" s="1" t="n">
+        <v>46248.4888023993</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>58.80499999999999</v>
+      </c>
+      <c r="I1166" t="n">
+        <v>5.00000000000001</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>BANEP</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>828.5</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>869.9250000000001</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>787.0749999999999</v>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr"/>
+      <c r="H1167" t="inlineStr"/>
+      <c r="I1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>84.2625</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>76.2375</v>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr"/>
+      <c r="H1168" t="inlineStr"/>
+      <c r="I1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>20.8845</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>18.8955</v>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr"/>
+      <c r="H1169" t="inlineStr"/>
+      <c r="I1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>43.71150000000001</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>39.5485</v>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr"/>
+      <c r="H1170" t="inlineStr"/>
+      <c r="I1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>5838</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>5282</v>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr"/>
+      <c r="H1171" t="inlineStr"/>
+      <c r="I1171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1171"/>
+  <dimension ref="A1:I1176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38638,9 +38638,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1158" t="inlineStr"/>
-      <c r="H1158" t="inlineStr"/>
-      <c r="I1158" t="inlineStr"/>
+      <c r="G1158" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>2916</v>
+      </c>
+      <c r="I1158" t="n">
+        <v>9.229571984435797</v>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" s="1" t="n">
@@ -38732,7 +38738,7 @@
         </is>
       </c>
       <c r="G1161" s="1" t="n">
-        <v>46248.4888023993</v>
+        <v>46248.48880239583</v>
       </c>
       <c r="H1161" t="n">
         <v>26.7235</v>
@@ -38765,7 +38771,7 @@
         </is>
       </c>
       <c r="G1162" s="1" t="n">
-        <v>46248.4888023993</v>
+        <v>46248.48880239583</v>
       </c>
       <c r="H1162" t="n">
         <v>874.4749999999999</v>
@@ -38797,9 +38803,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1163" t="inlineStr"/>
-      <c r="H1163" t="inlineStr"/>
-      <c r="I1163" t="inlineStr"/>
+      <c r="G1163" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>5327</v>
+      </c>
+      <c r="I1163" t="n">
+        <v>4.499820724273933</v>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" s="1" t="n">
@@ -38824,9 +38836,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1164" t="inlineStr"/>
-      <c r="H1164" t="inlineStr"/>
-      <c r="I1164" t="inlineStr"/>
+      <c r="G1164" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>4262.5</v>
+      </c>
+      <c r="I1164" t="n">
+        <v>8.569283569283568</v>
+      </c>
     </row>
     <row r="1165">
       <c r="A1165" s="1" t="n">
@@ -38852,7 +38870,7 @@
         </is>
       </c>
       <c r="G1165" s="1" t="n">
-        <v>46248.4888023993</v>
+        <v>46248.48880239583</v>
       </c>
       <c r="H1165" t="n">
         <v>20.273</v>
@@ -38885,7 +38903,7 @@
         </is>
       </c>
       <c r="G1166" s="1" t="n">
-        <v>46248.4888023993</v>
+        <v>46248.48880239583</v>
       </c>
       <c r="H1166" t="n">
         <v>58.80499999999999</v>
@@ -38917,9 +38935,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1167" t="inlineStr"/>
-      <c r="H1167" t="inlineStr"/>
-      <c r="I1167" t="inlineStr"/>
+      <c r="G1167" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>807</v>
+      </c>
+      <c r="I1167" t="n">
+        <v>2.595051297525649</v>
+      </c>
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
@@ -38944,9 +38968,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1168" t="inlineStr"/>
-      <c r="H1168" t="inlineStr"/>
-      <c r="I1168" t="inlineStr"/>
+      <c r="G1168" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="I1168" t="n">
+        <v>2.367601246105926</v>
+      </c>
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
@@ -38971,9 +39001,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1169" t="inlineStr"/>
-      <c r="H1169" t="inlineStr"/>
-      <c r="I1169" t="inlineStr"/>
+      <c r="G1169" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="I1169" t="n">
+        <v>6.234288587229774</v>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
@@ -38998,9 +39034,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1170" t="inlineStr"/>
-      <c r="H1170" t="inlineStr"/>
-      <c r="I1170" t="inlineStr"/>
+      <c r="G1170" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="I1170" t="n">
+        <v>0.888782128272891</v>
+      </c>
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
@@ -39025,9 +39067,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1171" t="inlineStr"/>
-      <c r="H1171" t="inlineStr"/>
-      <c r="I1171" t="inlineStr"/>
+      <c r="G1171" s="1" t="n">
+        <v>46251.46319393501</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>5327</v>
+      </c>
+      <c r="I1171" t="n">
+        <v>4.190647482014389</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>8.568000000000001</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>7.752</v>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+      <c r="H1172" t="inlineStr"/>
+      <c r="I1172" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>25.9665</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>23.4935</v>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr"/>
+      <c r="H1173" t="inlineStr"/>
+      <c r="I1173" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>5344</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>5611.2</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>5076.8</v>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr"/>
+      <c r="H1174" t="inlineStr"/>
+      <c r="I1174" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>4310</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>4525.5</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>4094.5</v>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr"/>
+      <c r="H1175" t="inlineStr"/>
+      <c r="I1175" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>20.235</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>21.24675</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>19.22325</v>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr"/>
+      <c r="H1176" t="inlineStr"/>
+      <c r="I1176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1176"/>
+  <dimension ref="A1:I1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38639,7 +38639,7 @@
         </is>
       </c>
       <c r="G1158" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1158" t="n">
         <v>2916</v>
@@ -38804,7 +38804,7 @@
         </is>
       </c>
       <c r="G1163" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1163" t="n">
         <v>5327</v>
@@ -38837,7 +38837,7 @@
         </is>
       </c>
       <c r="G1164" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1164" t="n">
         <v>4262.5</v>
@@ -38936,7 +38936,7 @@
         </is>
       </c>
       <c r="G1167" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1167" t="n">
         <v>807</v>
@@ -38969,7 +38969,7 @@
         </is>
       </c>
       <c r="G1168" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1168" t="n">
         <v>78.34999999999999</v>
@@ -39002,7 +39002,7 @@
         </is>
       </c>
       <c r="G1169" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1169" t="n">
         <v>18.65</v>
@@ -39035,7 +39035,7 @@
         </is>
       </c>
       <c r="G1170" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1170" t="n">
         <v>41.26</v>
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="G1171" s="1" t="n">
-        <v>46251.46319393501</v>
+        <v>46251.46319393518</v>
       </c>
       <c r="H1171" t="n">
         <v>5327</v>
@@ -39154,9 +39154,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1174" t="inlineStr"/>
-      <c r="H1174" t="inlineStr"/>
-      <c r="I1174" t="inlineStr"/>
+      <c r="G1174" s="1" t="n">
+        <v>46252.46024265928</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>5076.8</v>
+      </c>
+      <c r="I1174" t="n">
+        <v>4.999999999999996</v>
+      </c>
     </row>
     <row r="1175">
       <c r="A1175" s="1" t="n">
@@ -39208,9 +39214,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1176" t="inlineStr"/>
-      <c r="H1176" t="inlineStr"/>
-      <c r="I1176" t="inlineStr"/>
+      <c r="G1176" s="1" t="n">
+        <v>46252.46024265928</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>19.22325</v>
+      </c>
+      <c r="I1176" t="n">
+        <v>4.999999999999996</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>5100</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>5355</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>4845</v>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr"/>
+      <c r="H1177" t="inlineStr"/>
+      <c r="I1177" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>20.0025</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>18.0975</v>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr"/>
+      <c r="H1178" t="inlineStr"/>
+      <c r="I1178" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>18.984</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>17.176</v>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr"/>
+      <c r="H1179" t="inlineStr"/>
+      <c r="I1179" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>4222.5</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>4433.625</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>4011.375</v>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr"/>
+      <c r="H1180" t="inlineStr"/>
+      <c r="I1180" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>58.926</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>53.31399999999999</v>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr"/>
+      <c r="H1181" t="inlineStr"/>
+      <c r="I1181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1181"/>
+  <dimension ref="A1:I1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39127,9 +39127,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1173" t="inlineStr"/>
-      <c r="H1173" t="inlineStr"/>
-      <c r="I1173" t="inlineStr"/>
+      <c r="G1173" s="1" t="n">
+        <v>46253.45988168476</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>25.9665</v>
+      </c>
+      <c r="I1173" t="n">
+        <v>-4.999999999999997</v>
+      </c>
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
@@ -39155,7 +39161,7 @@
         </is>
       </c>
       <c r="G1174" s="1" t="n">
-        <v>46252.46024265928</v>
+        <v>46252.46024266204</v>
       </c>
       <c r="H1174" t="n">
         <v>5076.8</v>
@@ -39215,7 +39221,7 @@
         </is>
       </c>
       <c r="G1176" s="1" t="n">
-        <v>46252.46024265928</v>
+        <v>46252.46024266204</v>
       </c>
       <c r="H1176" t="n">
         <v>19.22325</v>
@@ -39247,9 +39253,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1177" t="inlineStr"/>
-      <c r="H1177" t="inlineStr"/>
-      <c r="I1177" t="inlineStr"/>
+      <c r="G1177" s="1" t="n">
+        <v>46253.45988168476</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>5355</v>
+      </c>
+      <c r="I1177" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="1178">
       <c r="A1178" s="1" t="n">
@@ -39274,9 +39286,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1178" t="inlineStr"/>
-      <c r="H1178" t="inlineStr"/>
-      <c r="I1178" t="inlineStr"/>
+      <c r="G1178" s="1" t="n">
+        <v>46253.45988168476</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>20.0025</v>
+      </c>
+      <c r="I1178" t="n">
+        <v>-5.000000000000003</v>
+      </c>
     </row>
     <row r="1179">
       <c r="A1179" s="1" t="n">
@@ -39301,9 +39319,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1179" t="inlineStr"/>
-      <c r="H1179" t="inlineStr"/>
-      <c r="I1179" t="inlineStr"/>
+      <c r="G1179" s="1" t="n">
+        <v>46253.45988168476</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>18.984</v>
+      </c>
+      <c r="I1179" t="n">
+        <v>-5.00000000000002</v>
+      </c>
     </row>
     <row r="1180">
       <c r="A1180" s="1" t="n">
@@ -39355,9 +39379,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1181" t="inlineStr"/>
-      <c r="H1181" t="inlineStr"/>
-      <c r="I1181" t="inlineStr"/>
+      <c r="G1181" s="1" t="n">
+        <v>46253.45988168476</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>58.926</v>
+      </c>
+      <c r="I1181" t="n">
+        <v>-5.000000000000008</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>20.8005</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>18.8195</v>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr"/>
+      <c r="H1182" t="inlineStr"/>
+      <c r="I1182" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>63.315</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>57.285</v>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr"/>
+      <c r="H1183" t="inlineStr"/>
+      <c r="I1183" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr"/>
+      <c r="H1184" t="inlineStr"/>
+      <c r="I1184" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>73.815</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>66.785</v>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr"/>
+      <c r="H1185" t="inlineStr"/>
+      <c r="I1185" t="inlineStr"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>26.715</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>28.05075</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>25.37925</v>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr"/>
+      <c r="H1186" t="inlineStr"/>
+      <c r="I1186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1186"/>
+  <dimension ref="A1:I1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39100,9 +39100,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1172" t="inlineStr"/>
-      <c r="H1172" t="inlineStr"/>
-      <c r="I1172" t="inlineStr"/>
+      <c r="G1172" s="1" t="n">
+        <v>46254.4618390216</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>8.345000000000001</v>
+      </c>
+      <c r="I1172" t="n">
+        <v>-2.267156862745104</v>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
@@ -39128,7 +39134,7 @@
         </is>
       </c>
       <c r="G1173" s="1" t="n">
-        <v>46253.45988168476</v>
+        <v>46253.45988168981</v>
       </c>
       <c r="H1173" t="n">
         <v>25.9665</v>
@@ -39193,9 +39199,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1175" t="inlineStr"/>
-      <c r="H1175" t="inlineStr"/>
-      <c r="I1175" t="inlineStr"/>
+      <c r="G1175" s="1" t="n">
+        <v>46254.4618390216</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>4287</v>
+      </c>
+      <c r="I1175" t="n">
+        <v>0.5336426914153133</v>
+      </c>
     </row>
     <row r="1176">
       <c r="A1176" s="1" t="n">
@@ -39254,7 +39266,7 @@
         </is>
       </c>
       <c r="G1177" s="1" t="n">
-        <v>46253.45988168476</v>
+        <v>46253.45988168981</v>
       </c>
       <c r="H1177" t="n">
         <v>5355</v>
@@ -39287,7 +39299,7 @@
         </is>
       </c>
       <c r="G1178" s="1" t="n">
-        <v>46253.45988168476</v>
+        <v>46253.45988168981</v>
       </c>
       <c r="H1178" t="n">
         <v>20.0025</v>
@@ -39320,7 +39332,7 @@
         </is>
       </c>
       <c r="G1179" s="1" t="n">
-        <v>46253.45988168476</v>
+        <v>46253.45988168981</v>
       </c>
       <c r="H1179" t="n">
         <v>18.984</v>
@@ -39380,7 +39392,7 @@
         </is>
       </c>
       <c r="G1181" s="1" t="n">
-        <v>46253.45988168476</v>
+        <v>46253.45988168981</v>
       </c>
       <c r="H1181" t="n">
         <v>58.926</v>
@@ -39466,9 +39478,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1184" t="inlineStr"/>
-      <c r="H1184" t="inlineStr"/>
-      <c r="I1184" t="inlineStr"/>
+      <c r="G1184" s="1" t="n">
+        <v>46254.4618390216</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="I1184" t="n">
+        <v>-5.000000000000016</v>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" s="1" t="n">
@@ -39523,6 +39541,141 @@
       <c r="G1186" t="inlineStr"/>
       <c r="H1186" t="inlineStr"/>
       <c r="I1186" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>5454</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>5726.7</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>5181.3</v>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr"/>
+      <c r="H1187" t="inlineStr"/>
+      <c r="I1187" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>128.31</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr"/>
+      <c r="H1188" t="inlineStr"/>
+      <c r="I1188" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr"/>
+      <c r="H1189" t="inlineStr"/>
+      <c r="I1189" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1190" t="n">
+        <v>4274</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>4487.7</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>4060.3</v>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr"/>
+      <c r="H1190" t="inlineStr"/>
+      <c r="I1190" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1191" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>44.7825</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>40.5175</v>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr"/>
+      <c r="H1191" t="inlineStr"/>
+      <c r="I1191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1191"/>
+  <dimension ref="A1:I1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="G1172" s="1" t="n">
-        <v>46254.4618390216</v>
+        <v>46254.46183901621</v>
       </c>
       <c r="H1172" t="n">
         <v>8.345000000000001</v>
@@ -39200,7 +39200,7 @@
         </is>
       </c>
       <c r="G1175" s="1" t="n">
-        <v>46254.4618390216</v>
+        <v>46254.46183901621</v>
       </c>
       <c r="H1175" t="n">
         <v>4287</v>
@@ -39364,9 +39364,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1180" t="inlineStr"/>
-      <c r="H1180" t="inlineStr"/>
-      <c r="I1180" t="inlineStr"/>
+      <c r="G1180" s="1" t="n">
+        <v>46255.46150741869</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>4141</v>
+      </c>
+      <c r="I1180" t="n">
+        <v>1.930136175251628</v>
+      </c>
     </row>
     <row r="1181">
       <c r="A1181" s="1" t="n">
@@ -39424,9 +39430,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1182" t="inlineStr"/>
-      <c r="H1182" t="inlineStr"/>
-      <c r="I1182" t="inlineStr"/>
+      <c r="G1182" s="1" t="n">
+        <v>46255.46150741869</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>18.8195</v>
+      </c>
+      <c r="I1182" t="n">
+        <v>4.999999999999987</v>
+      </c>
     </row>
     <row r="1183">
       <c r="A1183" s="1" t="n">
@@ -39451,9 +39463,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1183" t="inlineStr"/>
-      <c r="H1183" t="inlineStr"/>
-      <c r="I1183" t="inlineStr"/>
+      <c r="G1183" s="1" t="n">
+        <v>46255.46150741869</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>57.285</v>
+      </c>
+      <c r="I1183" t="n">
+        <v>5.000000000000001</v>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" s="1" t="n">
@@ -39479,7 +39497,7 @@
         </is>
       </c>
       <c r="G1184" s="1" t="n">
-        <v>46254.4618390216</v>
+        <v>46254.46183901621</v>
       </c>
       <c r="H1184" t="n">
         <v>21.42</v>
@@ -39538,9 +39556,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1186" t="inlineStr"/>
-      <c r="H1186" t="inlineStr"/>
-      <c r="I1186" t="inlineStr"/>
+      <c r="G1186" s="1" t="n">
+        <v>46255.46150741869</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>25.37925</v>
+      </c>
+      <c r="I1186" t="n">
+        <v>5.000000000000003</v>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" s="1" t="n">
@@ -39565,9 +39589,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1187" t="inlineStr"/>
-      <c r="H1187" t="inlineStr"/>
-      <c r="I1187" t="inlineStr"/>
+      <c r="G1187" s="1" t="n">
+        <v>46255.46150741869</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>5181.3</v>
+      </c>
+      <c r="I1187" t="n">
+        <v>4.999999999999996</v>
+      </c>
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
@@ -39676,6 +39706,141 @@
       <c r="G1191" t="inlineStr"/>
       <c r="H1191" t="inlineStr"/>
       <c r="I1191" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>25.655</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>26.93775</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>24.37225</v>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr"/>
+      <c r="H1192" t="inlineStr"/>
+      <c r="I1192" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>5304</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>5569.2</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>5038.8</v>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr"/>
+      <c r="H1193" t="inlineStr"/>
+      <c r="I1193" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr"/>
+      <c r="H1194" t="inlineStr"/>
+      <c r="I1194" t="inlineStr"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1195" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>60.438</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>54.682</v>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr"/>
+      <c r="H1195" t="inlineStr"/>
+      <c r="I1195" t="inlineStr"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>43.134</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>39.026</v>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr"/>
+      <c r="H1196" t="inlineStr"/>
+      <c r="I1196" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1196"/>
+  <dimension ref="A1:I1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="G1180" s="1" t="n">
-        <v>46255.46150741869</v>
+        <v>46255.46150741898</v>
       </c>
       <c r="H1180" t="n">
         <v>4141</v>
@@ -39431,7 +39431,7 @@
         </is>
       </c>
       <c r="G1182" s="1" t="n">
-        <v>46255.46150741869</v>
+        <v>46255.46150741898</v>
       </c>
       <c r="H1182" t="n">
         <v>18.8195</v>
@@ -39464,7 +39464,7 @@
         </is>
       </c>
       <c r="G1183" s="1" t="n">
-        <v>46255.46150741869</v>
+        <v>46255.46150741898</v>
       </c>
       <c r="H1183" t="n">
         <v>57.285</v>
@@ -39529,9 +39529,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1185" t="inlineStr"/>
-      <c r="H1185" t="inlineStr"/>
-      <c r="I1185" t="inlineStr"/>
+      <c r="G1185" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="I1185" t="n">
+        <v>2.90184921763868</v>
+      </c>
     </row>
     <row r="1186">
       <c r="A1186" s="1" t="n">
@@ -39557,7 +39563,7 @@
         </is>
       </c>
       <c r="G1186" s="1" t="n">
-        <v>46255.46150741869</v>
+        <v>46255.46150741898</v>
       </c>
       <c r="H1186" t="n">
         <v>25.37925</v>
@@ -39590,7 +39596,7 @@
         </is>
       </c>
       <c r="G1187" s="1" t="n">
-        <v>46255.46150741869</v>
+        <v>46255.46150741898</v>
       </c>
       <c r="H1187" t="n">
         <v>5181.3</v>
@@ -39622,9 +39628,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1188" t="inlineStr"/>
-      <c r="H1188" t="inlineStr"/>
-      <c r="I1188" t="inlineStr"/>
+      <c r="G1188" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>120.16</v>
+      </c>
+      <c r="I1188" t="n">
+        <v>1.669394435351887</v>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" s="1" t="n">
@@ -39649,9 +39661,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1189" t="inlineStr"/>
-      <c r="H1189" t="inlineStr"/>
-      <c r="I1189" t="inlineStr"/>
+      <c r="G1189" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>20.635</v>
+      </c>
+      <c r="I1189" t="n">
+        <v>2.665094339622631</v>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" s="1" t="n">
@@ -39676,9 +39694,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1190" t="inlineStr"/>
-      <c r="H1190" t="inlineStr"/>
-      <c r="I1190" t="inlineStr"/>
+      <c r="G1190" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>4175.5</v>
+      </c>
+      <c r="I1190" t="n">
+        <v>2.304632662611137</v>
+      </c>
     </row>
     <row r="1191">
       <c r="A1191" s="1" t="n">
@@ -39703,9 +39727,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1191" t="inlineStr"/>
-      <c r="H1191" t="inlineStr"/>
-      <c r="I1191" t="inlineStr"/>
+      <c r="G1191" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="I1191" t="n">
+        <v>7.104337631887459</v>
+      </c>
     </row>
     <row r="1192">
       <c r="A1192" s="1" t="n">
@@ -39730,9 +39760,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1192" t="inlineStr"/>
-      <c r="H1192" t="inlineStr"/>
-      <c r="I1192" t="inlineStr"/>
+      <c r="G1192" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="I1192" t="n">
+        <v>1.344767101929458</v>
+      </c>
     </row>
     <row r="1193">
       <c r="A1193" s="1" t="n">
@@ -39757,9 +39793,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1193" t="inlineStr"/>
-      <c r="H1193" t="inlineStr"/>
-      <c r="I1193" t="inlineStr"/>
+      <c r="G1193" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>5014</v>
+      </c>
+      <c r="I1193" t="n">
+        <v>5.467571644042232</v>
+      </c>
     </row>
     <row r="1194">
       <c r="A1194" s="1" t="n">
@@ -39784,9 +39826,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1194" t="inlineStr"/>
-      <c r="H1194" t="inlineStr"/>
-      <c r="I1194" t="inlineStr"/>
+      <c r="G1194" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="I1194" t="n">
+        <v>3.231707317073167</v>
+      </c>
     </row>
     <row r="1195">
       <c r="A1195" s="1" t="n">
@@ -39811,9 +39859,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1195" t="inlineStr"/>
-      <c r="H1195" t="inlineStr"/>
-      <c r="I1195" t="inlineStr"/>
+      <c r="G1195" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="I1195" t="n">
+        <v>2.95343988881168</v>
+      </c>
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
@@ -39838,9 +39892,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1196" t="inlineStr"/>
-      <c r="H1196" t="inlineStr"/>
-      <c r="I1196" t="inlineStr"/>
+      <c r="G1196" s="1" t="n">
+        <v>46258.46591039217</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="I1196" t="n">
+        <v>3.55404089581305</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>5213</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>5473.650000000001</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>4952.349999999999</v>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr"/>
+      <c r="H1197" t="inlineStr"/>
+      <c r="I1197" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1198" t="n">
+        <v>7.887</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>8.28135</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>7.492649999999999</v>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr"/>
+      <c r="H1198" t="inlineStr"/>
+      <c r="I1198" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>130.83</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>118.37</v>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr"/>
+      <c r="H1199" t="inlineStr"/>
+      <c r="I1199" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1200" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>22.428</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>20.292</v>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr"/>
+      <c r="H1200" t="inlineStr"/>
+      <c r="I1200" t="inlineStr"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1201" t="n">
+        <v>26.345</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>27.66225</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>25.02775</v>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr"/>
+      <c r="H1201" t="inlineStr"/>
+      <c r="I1201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1201"/>
+  <dimension ref="A1:I1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39530,7 +39530,7 @@
         </is>
       </c>
       <c r="G1185" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1185" t="n">
         <v>68.26000000000001</v>
@@ -39629,7 +39629,7 @@
         </is>
       </c>
       <c r="G1188" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1188" t="n">
         <v>120.16</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="G1189" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1189" t="n">
         <v>20.635</v>
@@ -39695,7 +39695,7 @@
         </is>
       </c>
       <c r="G1190" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1190" t="n">
         <v>4175.5</v>
@@ -39728,7 +39728,7 @@
         </is>
       </c>
       <c r="G1191" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1191" t="n">
         <v>39.62</v>
@@ -39761,7 +39761,7 @@
         </is>
       </c>
       <c r="G1192" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1192" t="n">
         <v>25.31</v>
@@ -39794,7 +39794,7 @@
         </is>
       </c>
       <c r="G1193" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1193" t="n">
         <v>5014</v>
@@ -39827,7 +39827,7 @@
         </is>
       </c>
       <c r="G1194" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1194" t="n">
         <v>31.74</v>
@@ -39860,7 +39860,7 @@
         </is>
       </c>
       <c r="G1195" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1195" t="n">
         <v>55.86</v>
@@ -39893,7 +39893,7 @@
         </is>
       </c>
       <c r="G1196" s="1" t="n">
-        <v>46258.46591039217</v>
+        <v>46258.46591039352</v>
       </c>
       <c r="H1196" t="n">
         <v>39.62</v>
@@ -39952,9 +39952,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1198" t="inlineStr"/>
-      <c r="H1198" t="inlineStr"/>
-      <c r="I1198" t="inlineStr"/>
+      <c r="G1198" s="1" t="n">
+        <v>46259.4631656065</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>7.492649999999999</v>
+      </c>
+      <c r="I1198" t="n">
+        <v>5.000000000000003</v>
+      </c>
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
@@ -40036,6 +40042,141 @@
       <c r="G1201" t="inlineStr"/>
       <c r="H1201" t="inlineStr"/>
       <c r="I1201" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1202" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>2415</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>2185</v>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr"/>
+      <c r="H1202" t="inlineStr"/>
+      <c r="I1202" t="inlineStr"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1203" t="n">
+        <v>7.145</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>7.50225</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>6.787749999999999</v>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr"/>
+      <c r="H1203" t="inlineStr"/>
+      <c r="I1203" t="inlineStr"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1204" t="n">
+        <v>5027</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>5278.35</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>4775.65</v>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr"/>
+      <c r="H1204" t="inlineStr"/>
+      <c r="I1204" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1205" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>71.44200000000001</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>64.63800000000001</v>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr"/>
+      <c r="H1205" t="inlineStr"/>
+      <c r="I1205" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>MGNT</t>
+        </is>
+      </c>
+      <c r="C1206" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>1575</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr"/>
+      <c r="H1206" t="inlineStr"/>
+      <c r="I1206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1206"/>
+  <dimension ref="A1:I1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39953,7 +39953,7 @@
         </is>
       </c>
       <c r="G1198" s="1" t="n">
-        <v>46259.4631656065</v>
+        <v>46259.46316560185</v>
       </c>
       <c r="H1198" t="n">
         <v>7.492649999999999</v>
@@ -40177,6 +40177,141 @@
       <c r="G1206" t="inlineStr"/>
       <c r="H1206" t="inlineStr"/>
       <c r="I1206" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>5129</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>5385.45</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>4872.55</v>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr"/>
+      <c r="H1207" t="inlineStr"/>
+      <c r="I1207" t="inlineStr"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>4237.5</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>4449.375</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>4025.625</v>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr"/>
+      <c r="H1208" t="inlineStr"/>
+      <c r="I1208" t="inlineStr"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1209" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr"/>
+      <c r="H1209" t="inlineStr"/>
+      <c r="I1209" t="inlineStr"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1210" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>69.699</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>63.06099999999999</v>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr"/>
+      <c r="H1210" t="inlineStr"/>
+      <c r="I1210" t="inlineStr"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>15.155</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>15.91275</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>14.39725</v>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr"/>
+      <c r="H1211" t="inlineStr"/>
+      <c r="I1211" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1211"/>
+  <dimension ref="A1:I1216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39925,9 +39925,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1197" t="inlineStr"/>
-      <c r="H1197" t="inlineStr"/>
-      <c r="I1197" t="inlineStr"/>
+      <c r="G1197" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>5102</v>
+      </c>
+      <c r="I1197" t="n">
+        <v>2.12929215422981</v>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
@@ -39985,9 +39991,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1199" t="inlineStr"/>
-      <c r="H1199" t="inlineStr"/>
-      <c r="I1199" t="inlineStr"/>
+      <c r="G1199" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="I1199" t="n">
+        <v>3.402889245585871</v>
+      </c>
     </row>
     <row r="1200">
       <c r="A1200" s="1" t="n">
@@ -40012,9 +40024,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1200" t="inlineStr"/>
-      <c r="H1200" t="inlineStr"/>
-      <c r="I1200" t="inlineStr"/>
+      <c r="G1200" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="I1200" t="n">
+        <v>3.370786516853927</v>
+      </c>
     </row>
     <row r="1201">
       <c r="A1201" s="1" t="n">
@@ -40039,9 +40057,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1201" t="inlineStr"/>
-      <c r="H1201" t="inlineStr"/>
-      <c r="I1201" t="inlineStr"/>
+      <c r="G1201" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>25.305</v>
+      </c>
+      <c r="I1201" t="n">
+        <v>3.947618143860312</v>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
@@ -40066,9 +40090,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1202" t="inlineStr"/>
-      <c r="H1202" t="inlineStr"/>
-      <c r="I1202" t="inlineStr"/>
+      <c r="G1202" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>2185</v>
+      </c>
+      <c r="I1202" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
@@ -40147,9 +40177,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1205" t="inlineStr"/>
-      <c r="H1205" t="inlineStr"/>
-      <c r="I1205" t="inlineStr"/>
+      <c r="G1205" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>64.63800000000001</v>
+      </c>
+      <c r="I1205" t="n">
+        <v>5.000000000000001</v>
+      </c>
     </row>
     <row r="1206">
       <c r="A1206" s="1" t="n">
@@ -40282,9 +40318,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1210" t="inlineStr"/>
-      <c r="H1210" t="inlineStr"/>
-      <c r="I1210" t="inlineStr"/>
+      <c r="G1210" s="1" t="n">
+        <v>46261.89039374796</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>63.06099999999999</v>
+      </c>
+      <c r="I1210" t="n">
+        <v>5.000000000000004</v>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" s="1" t="n">
@@ -40312,6 +40354,141 @@
       <c r="G1211" t="inlineStr"/>
       <c r="H1211" t="inlineStr"/>
       <c r="I1211" t="inlineStr"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1212" t="n">
+        <v>24.855</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>26.09775</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>23.61225</v>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr"/>
+      <c r="H1212" t="inlineStr"/>
+      <c r="I1212" t="inlineStr"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>19.745</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>20.73225</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>18.75775</v>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr"/>
+      <c r="H1213" t="inlineStr"/>
+      <c r="I1213" t="inlineStr"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1214" t="n">
+        <v>4996</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>5245.8</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>4746.2</v>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr"/>
+      <c r="H1214" t="inlineStr"/>
+      <c r="I1214" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1215" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>122.745</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>111.055</v>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr"/>
+      <c r="H1215" t="inlineStr"/>
+      <c r="I1215" t="inlineStr"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1216" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>32.025</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>28.975</v>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr"/>
+      <c r="H1216" t="inlineStr"/>
+      <c r="I1216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1216"/>
+  <dimension ref="A1:I1221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39926,7 +39926,7 @@
         </is>
       </c>
       <c r="G1197" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1197" t="n">
         <v>5102</v>
@@ -39992,7 +39992,7 @@
         </is>
       </c>
       <c r="G1199" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1199" t="n">
         <v>120.36</v>
@@ -40025,7 +40025,7 @@
         </is>
       </c>
       <c r="G1200" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1200" t="n">
         <v>20.64</v>
@@ -40058,7 +40058,7 @@
         </is>
       </c>
       <c r="G1201" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1201" t="n">
         <v>25.305</v>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="G1202" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1202" t="n">
         <v>2185</v>
@@ -40123,9 +40123,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1203" t="inlineStr"/>
-      <c r="H1203" t="inlineStr"/>
-      <c r="I1203" t="inlineStr"/>
+      <c r="G1203" s="1" t="n">
+        <v>46262.93848001114</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>7.427</v>
+      </c>
+      <c r="I1203" t="n">
+        <v>-3.946815955213437</v>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
@@ -40150,9 +40156,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1204" t="inlineStr"/>
-      <c r="H1204" t="inlineStr"/>
-      <c r="I1204" t="inlineStr"/>
+      <c r="G1204" s="1" t="n">
+        <v>46262.93848001114</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>5072</v>
+      </c>
+      <c r="I1204" t="n">
+        <v>-0.8951661030435647</v>
+      </c>
     </row>
     <row r="1205">
       <c r="A1205" s="1" t="n">
@@ -40178,7 +40190,7 @@
         </is>
       </c>
       <c r="G1205" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1205" t="n">
         <v>64.63800000000001</v>
@@ -40210,9 +40222,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1206" t="inlineStr"/>
-      <c r="H1206" t="inlineStr"/>
-      <c r="I1206" t="inlineStr"/>
+      <c r="G1206" s="1" t="n">
+        <v>46262.93848001114</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>1499.5</v>
+      </c>
+      <c r="I1206" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="1207">
       <c r="A1207" s="1" t="n">
@@ -40264,9 +40282,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1208" t="inlineStr"/>
-      <c r="H1208" t="inlineStr"/>
-      <c r="I1208" t="inlineStr"/>
+      <c r="G1208" s="1" t="n">
+        <v>46262.93848001114</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>4449.375</v>
+      </c>
+      <c r="I1208" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" s="1" t="n">
@@ -40319,7 +40343,7 @@
         </is>
       </c>
       <c r="G1210" s="1" t="n">
-        <v>46261.89039374796</v>
+        <v>46261.89039375</v>
       </c>
       <c r="H1210" t="n">
         <v>63.06099999999999</v>
@@ -40405,9 +40429,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1213" t="inlineStr"/>
-      <c r="H1213" t="inlineStr"/>
-      <c r="I1213" t="inlineStr"/>
+      <c r="G1213" s="1" t="n">
+        <v>46262.93848001114</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>20.73225</v>
+      </c>
+      <c r="I1213" t="n">
+        <v>-4.999999999999997</v>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" s="1" t="n">
@@ -40489,6 +40519,141 @@
       <c r="G1216" t="inlineStr"/>
       <c r="H1216" t="inlineStr"/>
       <c r="I1216" t="inlineStr"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1217" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>70.01400000000001</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>63.346</v>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr"/>
+      <c r="H1217" t="inlineStr"/>
+      <c r="I1217" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1218" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr"/>
+      <c r="H1218" t="inlineStr"/>
+      <c r="I1218" t="inlineStr"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1219" t="n">
+        <v>5115</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>5370.75</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>4859.25</v>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr"/>
+      <c r="H1219" t="inlineStr"/>
+      <c r="I1219" t="inlineStr"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>4308.5</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>4523.925</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>4093.075</v>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr"/>
+      <c r="H1220" t="inlineStr"/>
+      <c r="I1220" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>32.7075</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>29.5925</v>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr"/>
+      <c r="H1221" t="inlineStr"/>
+      <c r="I1221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1221"/>
+  <dimension ref="A1:I1226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="G1203" s="1" t="n">
-        <v>46262.93848001114</v>
+        <v>46262.93848001157</v>
       </c>
       <c r="H1203" t="n">
         <v>7.427</v>
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="G1204" s="1" t="n">
-        <v>46262.93848001114</v>
+        <v>46262.93848001157</v>
       </c>
       <c r="H1204" t="n">
         <v>5072</v>
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="G1206" s="1" t="n">
-        <v>46262.93848001114</v>
+        <v>46262.93848001157</v>
       </c>
       <c r="H1206" t="n">
         <v>1499.5</v>
@@ -40255,9 +40255,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1207" t="inlineStr"/>
-      <c r="H1207" t="inlineStr"/>
-      <c r="I1207" t="inlineStr"/>
+      <c r="G1207" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>5353</v>
+      </c>
+      <c r="I1207" t="n">
+        <v>-4.367323064924936</v>
+      </c>
     </row>
     <row r="1208">
       <c r="A1208" s="1" t="n">
@@ -40283,7 +40289,7 @@
         </is>
       </c>
       <c r="G1208" s="1" t="n">
-        <v>46262.93848001114</v>
+        <v>46262.93848001157</v>
       </c>
       <c r="H1208" t="n">
         <v>4449.375</v>
@@ -40315,9 +40321,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1209" t="inlineStr"/>
-      <c r="H1209" t="inlineStr"/>
-      <c r="I1209" t="inlineStr"/>
+      <c r="G1209" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="I1209" t="n">
+        <v>1.593137254901958</v>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" s="1" t="n">
@@ -40375,9 +40387,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1211" t="inlineStr"/>
-      <c r="H1211" t="inlineStr"/>
-      <c r="I1211" t="inlineStr"/>
+      <c r="G1211" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="I1211" t="n">
+        <v>2.408446057406798</v>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" s="1" t="n">
@@ -40402,9 +40420,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1212" t="inlineStr"/>
-      <c r="H1212" t="inlineStr"/>
-      <c r="I1212" t="inlineStr"/>
+      <c r="G1212" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>25.645</v>
+      </c>
+      <c r="I1212" t="n">
+        <v>-3.178434922550792</v>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" s="1" t="n">
@@ -40430,7 +40454,7 @@
         </is>
       </c>
       <c r="G1213" s="1" t="n">
-        <v>46262.93848001114</v>
+        <v>46262.93848001157</v>
       </c>
       <c r="H1213" t="n">
         <v>20.73225</v>
@@ -40462,9 +40486,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1214" t="inlineStr"/>
-      <c r="H1214" t="inlineStr"/>
-      <c r="I1214" t="inlineStr"/>
+      <c r="G1214" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>5353</v>
+      </c>
+      <c r="I1214" t="n">
+        <v>-7.145716573258606</v>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" s="1" t="n">
@@ -40489,9 +40519,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1215" t="inlineStr"/>
-      <c r="H1215" t="inlineStr"/>
-      <c r="I1215" t="inlineStr"/>
+      <c r="G1215" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="I1215" t="n">
+        <v>-7.014542343883651</v>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" s="1" t="n">
@@ -40516,9 +40552,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1216" t="inlineStr"/>
-      <c r="H1216" t="inlineStr"/>
-      <c r="I1216" t="inlineStr"/>
+      <c r="G1216" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="I1216" t="n">
+        <v>-2.196721311475415</v>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" s="1" t="n">
@@ -40543,9 +40585,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1217" t="inlineStr"/>
-      <c r="H1217" t="inlineStr"/>
-      <c r="I1217" t="inlineStr"/>
+      <c r="G1217" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="I1217" t="n">
+        <v>-1.859628074385115</v>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" s="1" t="n">
@@ -40570,9 +40618,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1218" t="inlineStr"/>
-      <c r="H1218" t="inlineStr"/>
-      <c r="I1218" t="inlineStr"/>
+      <c r="G1218" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="I1218" t="n">
+        <v>-3.543689320388334</v>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="1" t="n">
@@ -40597,9 +40651,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1219" t="inlineStr"/>
-      <c r="H1219" t="inlineStr"/>
-      <c r="I1219" t="inlineStr"/>
+      <c r="G1219" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>5353</v>
+      </c>
+      <c r="I1219" t="n">
+        <v>-4.652981427174976</v>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" s="1" t="n">
@@ -40624,9 +40684,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1220" t="inlineStr"/>
-      <c r="H1220" t="inlineStr"/>
-      <c r="I1220" t="inlineStr"/>
+      <c r="G1220" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>4621.5</v>
+      </c>
+      <c r="I1220" t="n">
+        <v>-7.264709295578507</v>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" s="1" t="n">
@@ -40651,9 +40717,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1221" t="inlineStr"/>
-      <c r="H1221" t="inlineStr"/>
-      <c r="I1221" t="inlineStr"/>
+      <c r="G1221" s="1" t="n">
+        <v>46265.76115592929</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="I1221" t="n">
+        <v>-0.06420545746389447</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>5070</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>5323.5</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>4816.5</v>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr"/>
+      <c r="H1222" t="inlineStr"/>
+      <c r="I1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>4580.5</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>4809.525000000001</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>4351.474999999999</v>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr"/>
+      <c r="H1223" t="inlineStr"/>
+      <c r="I1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>61.08900000000001</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>55.27099999999999</v>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr"/>
+      <c r="H1224" t="inlineStr"/>
+      <c r="I1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>500.3</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>525.3150000000001</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>475.285</v>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr"/>
+      <c r="H1225" t="inlineStr"/>
+      <c r="I1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1226" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>41.3385</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>37.4015</v>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr"/>
+      <c r="H1226" t="inlineStr"/>
+      <c r="I1226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1226"/>
+  <dimension ref="A1:I1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40256,7 +40256,7 @@
         </is>
       </c>
       <c r="G1207" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1207" t="n">
         <v>5353</v>
@@ -40322,7 +40322,7 @@
         </is>
       </c>
       <c r="G1209" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1209" t="n">
         <v>40.15</v>
@@ -40388,7 +40388,7 @@
         </is>
       </c>
       <c r="G1211" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1211" t="n">
         <v>14.79</v>
@@ -40421,7 +40421,7 @@
         </is>
       </c>
       <c r="G1212" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1212" t="n">
         <v>25.645</v>
@@ -40487,7 +40487,7 @@
         </is>
       </c>
       <c r="G1214" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1214" t="n">
         <v>5353</v>
@@ -40520,7 +40520,7 @@
         </is>
       </c>
       <c r="G1215" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1215" t="n">
         <v>125.1</v>
@@ -40553,7 +40553,7 @@
         </is>
       </c>
       <c r="G1216" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1216" t="n">
         <v>31.17</v>
@@ -40586,7 +40586,7 @@
         </is>
       </c>
       <c r="G1217" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1217" t="n">
         <v>67.92</v>
@@ -40619,7 +40619,7 @@
         </is>
       </c>
       <c r="G1218" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1218" t="n">
         <v>21.33</v>
@@ -40652,7 +40652,7 @@
         </is>
       </c>
       <c r="G1219" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1219" t="n">
         <v>5353</v>
@@ -40685,7 +40685,7 @@
         </is>
       </c>
       <c r="G1220" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1220" t="n">
         <v>4621.5</v>
@@ -40718,7 +40718,7 @@
         </is>
       </c>
       <c r="G1221" s="1" t="n">
-        <v>46265.76115592929</v>
+        <v>46265.76115592592</v>
       </c>
       <c r="H1221" t="n">
         <v>31.17</v>
@@ -40750,9 +40750,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1222" t="inlineStr"/>
-      <c r="H1222" t="inlineStr"/>
-      <c r="I1222" t="inlineStr"/>
+      <c r="G1222" s="1" t="n">
+        <v>46266.65268422502</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>5323.5</v>
+      </c>
+      <c r="I1222" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" s="1" t="n">
@@ -40831,9 +40837,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1225" t="inlineStr"/>
-      <c r="H1225" t="inlineStr"/>
-      <c r="I1225" t="inlineStr"/>
+      <c r="G1225" s="1" t="n">
+        <v>46266.65268422502</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>525.3150000000001</v>
+      </c>
+      <c r="I1225" t="n">
+        <v>-5.000000000000009</v>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" s="1" t="n">
@@ -40861,6 +40873,141 @@
       <c r="G1226" t="inlineStr"/>
       <c r="H1226" t="inlineStr"/>
       <c r="I1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>22.205</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>23.31525</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>21.09475</v>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr"/>
+      <c r="H1227" t="inlineStr"/>
+      <c r="I1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>74.235</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>67.16500000000001</v>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr"/>
+      <c r="H1228" t="inlineStr"/>
+      <c r="I1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>85.52250000000001</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>77.3775</v>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr"/>
+      <c r="H1229" t="inlineStr"/>
+      <c r="I1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>26.205</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>27.51525</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>24.89475</v>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr"/>
+      <c r="H1230" t="inlineStr"/>
+      <c r="I1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>20.4015</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>18.4585</v>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr"/>
+      <c r="H1231" t="inlineStr"/>
+      <c r="I1231" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1231"/>
+  <dimension ref="A1:I1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40751,7 +40751,7 @@
         </is>
       </c>
       <c r="G1222" s="1" t="n">
-        <v>46266.65268422502</v>
+        <v>46266.65268422454</v>
       </c>
       <c r="H1222" t="n">
         <v>5323.5</v>
@@ -40838,7 +40838,7 @@
         </is>
       </c>
       <c r="G1225" s="1" t="n">
-        <v>46266.65268422502</v>
+        <v>46266.65268422454</v>
       </c>
       <c r="H1225" t="n">
         <v>525.3150000000001</v>
@@ -41008,6 +41008,141 @@
       <c r="G1231" t="inlineStr"/>
       <c r="H1231" t="inlineStr"/>
       <c r="I1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>32.1825</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>29.1175</v>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr"/>
+      <c r="H1232" t="inlineStr"/>
+      <c r="I1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>60.795</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>55.005</v>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr"/>
+      <c r="H1233" t="inlineStr"/>
+      <c r="I1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>20.034</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>18.126</v>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr"/>
+      <c r="H1234" t="inlineStr"/>
+      <c r="I1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>15.645</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>14.155</v>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr"/>
+      <c r="H1235" t="inlineStr"/>
+      <c r="I1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>41.95800000000001</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>37.962</v>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr"/>
+      <c r="H1236" t="inlineStr"/>
+      <c r="I1236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1236"/>
+  <dimension ref="A1:I1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40783,9 +40783,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1223" t="inlineStr"/>
-      <c r="H1223" t="inlineStr"/>
-      <c r="I1223" t="inlineStr"/>
+      <c r="G1223" s="1" t="n">
+        <v>46268.63342007014</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>4913.5</v>
+      </c>
+      <c r="I1223" t="n">
+        <v>-7.269948695557253</v>
+      </c>
     </row>
     <row r="1224">
       <c r="A1224" s="1" t="n">
@@ -40810,9 +40816,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1224" t="inlineStr"/>
-      <c r="H1224" t="inlineStr"/>
-      <c r="I1224" t="inlineStr"/>
+      <c r="G1224" s="1" t="n">
+        <v>46268.63342007014</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="I1224" t="n">
+        <v>-5.878308697146789</v>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" s="1" t="n">
@@ -40870,9 +40882,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1226" t="inlineStr"/>
-      <c r="H1226" t="inlineStr"/>
-      <c r="I1226" t="inlineStr"/>
+      <c r="G1226" s="1" t="n">
+        <v>46268.63342007014</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="I1226" t="n">
+        <v>-4.36880873761749</v>
+      </c>
     </row>
     <row r="1227">
       <c r="A1227" s="1" t="n">
@@ -41059,9 +41077,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1233" t="inlineStr"/>
-      <c r="H1233" t="inlineStr"/>
-      <c r="I1233" t="inlineStr"/>
+      <c r="G1233" s="1" t="n">
+        <v>46268.63342007014</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>60.795</v>
+      </c>
+      <c r="I1233" t="n">
+        <v>-5.000000000000006</v>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" s="1" t="n">
@@ -41086,9 +41110,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1234" t="inlineStr"/>
-      <c r="H1234" t="inlineStr"/>
-      <c r="I1234" t="inlineStr"/>
+      <c r="G1234" s="1" t="n">
+        <v>46268.63342007014</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>20.034</v>
+      </c>
+      <c r="I1234" t="n">
+        <v>-5.000000000000004</v>
+      </c>
     </row>
     <row r="1235">
       <c r="A1235" s="1" t="n">
@@ -41143,6 +41173,141 @@
       <c r="G1236" t="inlineStr"/>
       <c r="H1236" t="inlineStr"/>
       <c r="I1236" t="inlineStr"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>63</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>57</v>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr"/>
+      <c r="H1237" t="inlineStr"/>
+      <c r="I1237" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>5838</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>5282</v>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr"/>
+      <c r="H1238" t="inlineStr"/>
+      <c r="I1238" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>74.86499999999999</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>67.735</v>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr"/>
+      <c r="H1239" t="inlineStr"/>
+      <c r="I1239" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>129.38</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>135.849</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>122.911</v>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr"/>
+      <c r="H1240" t="inlineStr"/>
+      <c r="I1240" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>4786.5</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>5025.825</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>4547.175</v>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr"/>
+      <c r="I1241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1241"/>
+  <dimension ref="A1:I1246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40784,7 +40784,7 @@
         </is>
       </c>
       <c r="G1223" s="1" t="n">
-        <v>46268.63342007014</v>
+        <v>46268.63342006945</v>
       </c>
       <c r="H1223" t="n">
         <v>4913.5</v>
@@ -40817,7 +40817,7 @@
         </is>
       </c>
       <c r="G1224" s="1" t="n">
-        <v>46268.63342007014</v>
+        <v>46268.63342006945</v>
       </c>
       <c r="H1224" t="n">
         <v>61.6</v>
@@ -40883,7 +40883,7 @@
         </is>
       </c>
       <c r="G1226" s="1" t="n">
-        <v>46268.63342007014</v>
+        <v>46268.63342006945</v>
       </c>
       <c r="H1226" t="n">
         <v>41.09</v>
@@ -40915,9 +40915,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1227" t="inlineStr"/>
-      <c r="H1227" t="inlineStr"/>
-      <c r="I1227" t="inlineStr"/>
+      <c r="G1227" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="I1227" t="n">
+        <v>-6.147264129700527</v>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" s="1" t="n">
@@ -40942,9 +40948,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1228" t="inlineStr"/>
-      <c r="H1228" t="inlineStr"/>
-      <c r="I1228" t="inlineStr"/>
+      <c r="G1228" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="I1228" t="n">
+        <v>-4.554455445544553</v>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" s="1" t="n">
@@ -40969,9 +40981,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1229" t="inlineStr"/>
-      <c r="H1229" t="inlineStr"/>
-      <c r="I1229" t="inlineStr"/>
+      <c r="G1229" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="I1229" t="n">
+        <v>-1.534683855125844</v>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" s="1" t="n">
@@ -40996,9 +41014,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1230" t="inlineStr"/>
-      <c r="H1230" t="inlineStr"/>
-      <c r="I1230" t="inlineStr"/>
+      <c r="G1230" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="I1230" t="n">
+        <v>-3.720663995420727</v>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" s="1" t="n">
@@ -41023,9 +41047,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1231" t="inlineStr"/>
-      <c r="H1231" t="inlineStr"/>
-      <c r="I1231" t="inlineStr"/>
+      <c r="G1231" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="I1231" t="n">
+        <v>-6.484817292846122</v>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" s="1" t="n">
@@ -41050,9 +41080,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1232" t="inlineStr"/>
-      <c r="H1232" t="inlineStr"/>
-      <c r="I1232" t="inlineStr"/>
+      <c r="G1232" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>32.1825</v>
+      </c>
+      <c r="I1232" t="n">
+        <v>-4.999999999999996</v>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" s="1" t="n">
@@ -41078,7 +41114,7 @@
         </is>
       </c>
       <c r="G1233" s="1" t="n">
-        <v>46268.63342007014</v>
+        <v>46268.63342006945</v>
       </c>
       <c r="H1233" t="n">
         <v>60.795</v>
@@ -41111,7 +41147,7 @@
         </is>
       </c>
       <c r="G1234" s="1" t="n">
-        <v>46268.63342007014</v>
+        <v>46268.63342006945</v>
       </c>
       <c r="H1234" t="n">
         <v>20.034</v>
@@ -41143,9 +41179,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1235" t="inlineStr"/>
-      <c r="H1235" t="inlineStr"/>
-      <c r="I1235" t="inlineStr"/>
+      <c r="G1235" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>15.645</v>
+      </c>
+      <c r="I1235" t="n">
+        <v>-4.999999999999995</v>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" s="1" t="n">
@@ -41170,9 +41212,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1236" t="inlineStr"/>
-      <c r="H1236" t="inlineStr"/>
-      <c r="I1236" t="inlineStr"/>
+      <c r="G1236" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>41.95800000000001</v>
+      </c>
+      <c r="I1236" t="n">
+        <v>-5.000000000000029</v>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" s="1" t="n">
@@ -41224,9 +41272,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1238" t="inlineStr"/>
-      <c r="H1238" t="inlineStr"/>
-      <c r="I1238" t="inlineStr"/>
+      <c r="G1238" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1238" t="n">
+        <v>5838</v>
+      </c>
+      <c r="I1238" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" s="1" t="n">
@@ -41251,9 +41305,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1239" t="inlineStr"/>
-      <c r="H1239" t="inlineStr"/>
-      <c r="I1239" t="inlineStr"/>
+      <c r="G1239" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>74.86499999999999</v>
+      </c>
+      <c r="I1239" t="n">
+        <v>-4.999999999999996</v>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" s="1" t="n">
@@ -41305,9 +41365,150 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1241" t="inlineStr"/>
-      <c r="H1241" t="inlineStr"/>
-      <c r="I1241" t="inlineStr"/>
+      <c r="G1241" s="1" t="n">
+        <v>46269.63415089149</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>5025.825</v>
+      </c>
+      <c r="I1241" t="n">
+        <v>-4.999999999999996</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>2720</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>2856</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>2584</v>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr"/>
+      <c r="I1242" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>21.8925</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>19.8075</v>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr"/>
+      <c r="H1243" t="inlineStr"/>
+      <c r="I1243" t="inlineStr"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr"/>
+      <c r="I1244" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>7.782</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>8.171100000000001</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>7.3929</v>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr"/>
+      <c r="H1245" t="inlineStr"/>
+      <c r="I1245" t="inlineStr"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>77.952</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>70.52799999999999</v>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr"/>
+      <c r="H1246" t="inlineStr"/>
+      <c r="I1246" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1246"/>
+  <dimension ref="A1:I1255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40916,7 +40916,7 @@
         </is>
       </c>
       <c r="G1227" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1227" t="n">
         <v>23.57</v>
@@ -40949,7 +40949,7 @@
         </is>
       </c>
       <c r="G1228" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1228" t="n">
         <v>73.92</v>
@@ -40982,7 +40982,7 @@
         </is>
       </c>
       <c r="G1229" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1229" t="n">
         <v>82.7</v>
@@ -41015,7 +41015,7 @@
         </is>
       </c>
       <c r="G1230" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1230" t="n">
         <v>27.18</v>
@@ -41048,7 +41048,7 @@
         </is>
       </c>
       <c r="G1231" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1231" t="n">
         <v>20.69</v>
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="G1232" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1232" t="n">
         <v>32.1825</v>
@@ -41180,7 +41180,7 @@
         </is>
       </c>
       <c r="G1235" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1235" t="n">
         <v>15.645</v>
@@ -41213,7 +41213,7 @@
         </is>
       </c>
       <c r="G1236" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1236" t="n">
         <v>41.95800000000001</v>
@@ -41245,9 +41245,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1237" t="inlineStr"/>
-      <c r="H1237" t="inlineStr"/>
-      <c r="I1237" t="inlineStr"/>
+      <c r="G1237" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="I1237" t="n">
+        <v>-2.966666666666669</v>
+      </c>
     </row>
     <row r="1238">
       <c r="A1238" s="1" t="n">
@@ -41273,7 +41279,7 @@
         </is>
       </c>
       <c r="G1238" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1238" t="n">
         <v>5838</v>
@@ -41306,7 +41312,7 @@
         </is>
       </c>
       <c r="G1239" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1239" t="n">
         <v>74.86499999999999</v>
@@ -41338,9 +41344,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1240" t="inlineStr"/>
-      <c r="H1240" t="inlineStr"/>
-      <c r="I1240" t="inlineStr"/>
+      <c r="G1240" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>130.98</v>
+      </c>
+      <c r="I1240" t="n">
+        <v>-1.236667181944655</v>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" s="1" t="n">
@@ -41366,7 +41378,7 @@
         </is>
       </c>
       <c r="G1241" s="1" t="n">
-        <v>46269.63415089149</v>
+        <v>46269.6341508912</v>
       </c>
       <c r="H1241" t="n">
         <v>5025.825</v>
@@ -41398,9 +41410,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1242" t="inlineStr"/>
-      <c r="H1242" t="inlineStr"/>
-      <c r="I1242" t="inlineStr"/>
+      <c r="G1242" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>2682.5</v>
+      </c>
+      <c r="I1242" t="n">
+        <v>1.378676470588235</v>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" s="1" t="n">
@@ -41425,9 +41443,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1243" t="inlineStr"/>
-      <c r="H1243" t="inlineStr"/>
-      <c r="I1243" t="inlineStr"/>
+      <c r="G1243" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="I1243" t="n">
+        <v>1.534772182254198</v>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" s="1" t="n">
@@ -41452,9 +41476,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1244" t="inlineStr"/>
-      <c r="H1244" t="inlineStr"/>
-      <c r="I1244" t="inlineStr"/>
+      <c r="G1244" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="I1244" t="n">
+        <v>-1.151515151515159</v>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="1" t="n">
@@ -41479,9 +41509,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1245" t="inlineStr"/>
-      <c r="H1245" t="inlineStr"/>
-      <c r="I1245" t="inlineStr"/>
+      <c r="G1245" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="I1245" t="n">
+        <v>0.07710100231303299</v>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" s="1" t="n">
@@ -41506,9 +41542,258 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1246" t="inlineStr"/>
-      <c r="H1246" t="inlineStr"/>
-      <c r="I1246" t="inlineStr"/>
+      <c r="G1246" s="1" t="n">
+        <v>46272.69218805343</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="I1246" t="n">
+        <v>0.02693965517240844</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>CHMF</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>666.6</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>633.27</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>719.9280000000001</v>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr"/>
+      <c r="H1247" t="inlineStr"/>
+      <c r="I1247" t="inlineStr"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>NVTK</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>967.0999999999999</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1099.44</v>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr"/>
+      <c r="H1248" t="inlineStr"/>
+      <c r="I1248" t="inlineStr"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>99.14400000000001</v>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr"/>
+      <c r="H1249" t="inlineStr"/>
+      <c r="I1249" t="inlineStr"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1250" t="n">
+        <v>5049</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>4796.55</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>5452.92</v>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr"/>
+      <c r="H1250" t="inlineStr"/>
+      <c r="I1250" t="inlineStr"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1251" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>6132</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>5548</v>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr"/>
+      <c r="H1251" t="inlineStr"/>
+      <c r="I1251" t="inlineStr"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1252" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>35.805</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>32.395</v>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr"/>
+      <c r="H1252" t="inlineStr"/>
+      <c r="I1252" t="inlineStr"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>PIKK</t>
+        </is>
+      </c>
+      <c r="C1253" t="n">
+        <v>552.2</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>579.8100000000001</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>524.59</v>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr"/>
+      <c r="H1253" t="inlineStr"/>
+      <c r="I1253" t="inlineStr"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>83</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr"/>
+      <c r="H1254" t="inlineStr"/>
+      <c r="I1254" t="inlineStr"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>63.92400000000001</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>57.836</v>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr"/>
+      <c r="H1255" t="inlineStr"/>
+      <c r="I1255" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1255"/>
+  <dimension ref="A1:I1261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41246,7 +41246,7 @@
         </is>
       </c>
       <c r="G1237" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1237" t="n">
         <v>61.78</v>
@@ -41345,7 +41345,7 @@
         </is>
       </c>
       <c r="G1240" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1240" t="n">
         <v>130.98</v>
@@ -41411,7 +41411,7 @@
         </is>
       </c>
       <c r="G1242" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1242" t="n">
         <v>2682.5</v>
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="G1243" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1243" t="n">
         <v>20.53</v>
@@ -41477,7 +41477,7 @@
         </is>
       </c>
       <c r="G1244" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1244" t="n">
         <v>33.38</v>
@@ -41510,7 +41510,7 @@
         </is>
       </c>
       <c r="G1245" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1245" t="n">
         <v>7.776</v>
@@ -41543,7 +41543,7 @@
         </is>
       </c>
       <c r="G1246" s="1" t="n">
-        <v>46272.69218805343</v>
+        <v>46272.69218805555</v>
       </c>
       <c r="H1246" t="n">
         <v>74.22</v>
@@ -41683,9 +41683,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1251" t="inlineStr"/>
-      <c r="H1251" t="inlineStr"/>
-      <c r="I1251" t="inlineStr"/>
+      <c r="G1251" s="1" t="n">
+        <v>46273.63482998752</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>5548</v>
+      </c>
+      <c r="I1251" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" s="1" t="n">
@@ -41794,6 +41800,168 @@
       <c r="G1255" t="inlineStr"/>
       <c r="H1255" t="inlineStr"/>
       <c r="I1255" t="inlineStr"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>SNGSP</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>42.025</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>39.92375</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>45.387</v>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr"/>
+      <c r="H1256" t="inlineStr"/>
+      <c r="I1256" t="inlineStr"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1257" t="n">
+        <v>5567</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>5845.35</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>5288.65</v>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr"/>
+      <c r="H1257" t="inlineStr"/>
+      <c r="I1257" t="inlineStr"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>ROSN</t>
+        </is>
+      </c>
+      <c r="C1258" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>317.87</v>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr"/>
+      <c r="H1258" t="inlineStr"/>
+      <c r="I1258" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1259" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>44.121</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>39.919</v>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr"/>
+      <c r="H1259" t="inlineStr"/>
+      <c r="I1259" t="inlineStr"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>RNFT</t>
+        </is>
+      </c>
+      <c r="C1260" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>88.30499999999999</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>79.895</v>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr"/>
+      <c r="H1260" t="inlineStr"/>
+      <c r="I1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1261" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>78.624</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>71.136</v>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr"/>
+      <c r="H1261" t="inlineStr"/>
+      <c r="I1261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1261"/>
+  <dimension ref="A1:I1266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41684,7 +41684,7 @@
         </is>
       </c>
       <c r="G1251" s="1" t="n">
-        <v>46273.63482998752</v>
+        <v>46273.63482998843</v>
       </c>
       <c r="H1251" t="n">
         <v>5548</v>
@@ -41962,6 +41962,141 @@
       <c r="G1261" t="inlineStr"/>
       <c r="H1261" t="inlineStr"/>
       <c r="I1261" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>5506</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>5781.3</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>5230.7</v>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr"/>
+      <c r="H1262" t="inlineStr"/>
+      <c r="I1262" t="inlineStr"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>22.491</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>20.349</v>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr"/>
+      <c r="H1263" t="inlineStr"/>
+      <c r="I1263" t="inlineStr"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>23.015</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>24.16575</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>21.86425</v>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr"/>
+      <c r="H1264" t="inlineStr"/>
+      <c r="I1264" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>RTKM</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>43.74299999999999</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>39.577</v>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr"/>
+      <c r="H1265" t="inlineStr"/>
+      <c r="I1265" t="inlineStr"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>NLMK</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>77.616</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>70.224</v>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr"/>
+      <c r="H1266" t="inlineStr"/>
+      <c r="I1266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1266"/>
+  <dimension ref="A1:I1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41575,9 +41575,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1247" t="inlineStr"/>
-      <c r="H1247" t="inlineStr"/>
-      <c r="I1247" t="inlineStr"/>
+      <c r="G1247" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>647</v>
+      </c>
+      <c r="I1247" t="n">
+        <v>-2.940294029402943</v>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" s="1" t="n">
@@ -41602,9 +41608,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1248" t="inlineStr"/>
-      <c r="H1248" t="inlineStr"/>
-      <c r="I1248" t="inlineStr"/>
+      <c r="G1248" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>980.8</v>
+      </c>
+      <c r="I1248" t="n">
+        <v>-3.65422396856582</v>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" s="1" t="n">
@@ -41629,9 +41641,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1249" t="inlineStr"/>
-      <c r="H1249" t="inlineStr"/>
-      <c r="I1249" t="inlineStr"/>
+      <c r="G1249" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="I1249" t="n">
+        <v>-2.63616557734205</v>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" s="1" t="n">
@@ -41656,9 +41674,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1250" t="inlineStr"/>
-      <c r="H1250" t="inlineStr"/>
-      <c r="I1250" t="inlineStr"/>
+      <c r="G1250" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>5255</v>
+      </c>
+      <c r="I1250" t="n">
+        <v>4.080015844721728</v>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" s="1" t="n">
@@ -41716,9 +41740,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1252" t="inlineStr"/>
-      <c r="H1252" t="inlineStr"/>
-      <c r="I1252" t="inlineStr"/>
+      <c r="G1252" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="I1252" t="n">
+        <v>3.929618768328456</v>
+      </c>
     </row>
     <row r="1253">
       <c r="A1253" s="1" t="n">
@@ -41743,9 +41773,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1253" t="inlineStr"/>
-      <c r="H1253" t="inlineStr"/>
-      <c r="I1253" t="inlineStr"/>
+      <c r="G1253" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>533.1</v>
+      </c>
+      <c r="I1253" t="n">
+        <v>3.458891705903662</v>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" s="1" t="n">
@@ -41770,9 +41806,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1254" t="inlineStr"/>
-      <c r="H1254" t="inlineStr"/>
-      <c r="I1254" t="inlineStr"/>
+      <c r="G1254" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I1254" t="n">
+        <v>-3.373493975903611</v>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" s="1" t="n">
@@ -41797,9 +41839,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1255" t="inlineStr"/>
-      <c r="H1255" t="inlineStr"/>
-      <c r="I1255" t="inlineStr"/>
+      <c r="G1255" s="1" t="n">
+        <v>46275.63838647657</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>60</v>
+      </c>
+      <c r="I1255" t="n">
+        <v>1.445466491458611</v>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" s="1" t="n">
@@ -42097,6 +42145,141 @@
       <c r="G1266" t="inlineStr"/>
       <c r="H1266" t="inlineStr"/>
       <c r="I1266" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>PHOR</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>5466</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>5739.3</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>5192.7</v>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr"/>
+      <c r="H1267" t="inlineStr"/>
+      <c r="I1267" t="inlineStr"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>5186.5</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>5445.825</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>4927.175</v>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr"/>
+      <c r="H1268" t="inlineStr"/>
+      <c r="I1268" t="inlineStr"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>ALRS</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>21.6615</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>19.5985</v>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr"/>
+      <c r="H1269" t="inlineStr"/>
+      <c r="I1269" t="inlineStr"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>22.525</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>23.65125</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>21.39875</v>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr"/>
+      <c r="H1270" t="inlineStr"/>
+      <c r="I1270" t="inlineStr"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>TRMK</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr"/>
+      <c r="H1271" t="inlineStr"/>
+      <c r="I1271" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trades.xlsx
+++ b/data/trades.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1271"/>
+  <dimension ref="A1:I1281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41576,7 +41576,7 @@
         </is>
       </c>
       <c r="G1247" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1247" t="n">
         <v>647</v>
@@ -41609,7 +41609,7 @@
         </is>
       </c>
       <c r="G1248" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1248" t="n">
         <v>980.8</v>
@@ -41642,7 +41642,7 @@
         </is>
       </c>
       <c r="G1249" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1249" t="n">
         <v>89.38</v>
@@ -41675,7 +41675,7 @@
         </is>
       </c>
       <c r="G1250" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1250" t="n">
         <v>5255</v>
@@ -41741,7 +41741,7 @@
         </is>
       </c>
       <c r="G1252" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1252" t="n">
         <v>32.76</v>
@@ -41774,7 +41774,7 @@
         </is>
       </c>
       <c r="G1253" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1253" t="n">
         <v>533.1</v>
@@ -41807,7 +41807,7 @@
         </is>
       </c>
       <c r="G1254" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1254" t="n">
         <v>85.8</v>
@@ -41840,7 +41840,7 @@
         </is>
       </c>
       <c r="G1255" s="1" t="n">
-        <v>46275.63838647657</v>
+        <v>46275.63838648148</v>
       </c>
       <c r="H1255" t="n">
         <v>60</v>
@@ -41872,9 +41872,15 @@
           <t>Buy</t>
         </is>
       </c>
-      <c r="G1256" t="inlineStr"/>
-      <c r="H1256" t="inlineStr"/>
-      <c r="I1256" t="inlineStr"/>
+      <c r="G1256" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>41.605</v>
+      </c>
+      <c r="I1256" t="n">
+        <v>-0.9994051160023837</v>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" s="1" t="n">
@@ -41899,9 +41905,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1257" t="inlineStr"/>
-      <c r="H1257" t="inlineStr"/>
-      <c r="I1257" t="inlineStr"/>
+      <c r="G1257" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>5526</v>
+      </c>
+      <c r="I1257" t="n">
+        <v>0.7364828453386024</v>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" s="1" t="n">
@@ -41926,9 +41938,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1258" t="inlineStr"/>
-      <c r="H1258" t="inlineStr"/>
-      <c r="I1258" t="inlineStr"/>
+      <c r="G1258" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="I1258" t="n">
+        <v>-4.213986849970103</v>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" s="1" t="n">
@@ -41953,9 +41971,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1259" t="inlineStr"/>
-      <c r="H1259" t="inlineStr"/>
-      <c r="I1259" t="inlineStr"/>
+      <c r="G1259" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="I1259" t="n">
+        <v>4.164683484055211</v>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" s="1" t="n">
@@ -41980,9 +42004,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1260" t="inlineStr"/>
-      <c r="H1260" t="inlineStr"/>
-      <c r="I1260" t="inlineStr"/>
+      <c r="G1260" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I1260" t="n">
+        <v>-0.5945303210463734</v>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" s="1" t="n">
@@ -42007,9 +42037,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1261" t="inlineStr"/>
-      <c r="H1261" t="inlineStr"/>
-      <c r="I1261" t="inlineStr"/>
+      <c r="G1261" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="I1261" t="n">
+        <v>4.166666666666654</v>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" s="1" t="n">
@@ -42061,9 +42097,15 @@
           <t>Sell</t>
         </is>
       </c>
-      <c r="G1263" t="inlineStr"/>
-      <c r="H1263" t="inlineStr"/>
-      <c r="I1263" t="inlineStr"/>
+      <c r="G1263" s="1" t="n">
+        <v>46276.63760464759</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>20.349</v>
+      </c>
+      <c r="I1263" t="n">
+        <v>5.000000000000006</v>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" s="1" t="n">
@@ -42280,6 +42322,276 @@
       <c r="G1271" t="inlineStr"/>
       <c r="H1271" t="inlineStr"/>
       <c r="I1271" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>MGNT</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>1636.5</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>1554.675</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>1767.42</v>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr"/>
+      <c r="H1272" t="inlineStr"/>
+      <c r="I1272" t="inlineStr"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>TATN</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>629.4</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>597.9299999999999</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>679.7520000000001</v>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr"/>
+      <c r="H1273" t="inlineStr"/>
+      <c r="I1273" t="inlineStr"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>ENPG</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>294.595</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>334.9080000000001</v>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr"/>
+      <c r="H1274" t="inlineStr"/>
+      <c r="I1274" t="inlineStr"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>MAGN</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>21.6695</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>24.6348</v>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr"/>
+      <c r="H1275" t="inlineStr"/>
+      <c r="I1275" t="inlineStr"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>SBER</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>285</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr"/>
+      <c r="H1276" t="inlineStr"/>
+      <c r="I1276" t="inlineStr"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>AFLT</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr"/>
+      <c r="H1277" t="inlineStr"/>
+      <c r="I1277" t="inlineStr"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>RUAL</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>28.0245</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>25.3555</v>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr"/>
+      <c r="H1278" t="inlineStr"/>
+      <c r="I1278" t="inlineStr"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>AFKS</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>7.603</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>7.98315</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>7.222849999999999</v>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr"/>
+      <c r="H1279" t="inlineStr"/>
+      <c r="I1279" t="inlineStr"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>GMKN</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>132.34</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>138.957</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>125.723</v>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr"/>
+      <c r="H1280" t="inlineStr"/>
+      <c r="I1280" t="inlineStr"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>OZON</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>2569.5</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>2697.975</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>2441.025</v>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr"/>
+      <c r="H1281" t="inlineStr"/>
+      <c r="I1281" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
